--- a/data/trans_orig/P32-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P32-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han pensado que deberían beber menos en 2007</t>
+          <t>Población según si han pensado que deberían beber menos en 2007 (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1353</t>
+          <t>1701</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11686</t>
+          <t>11413</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11183</t>
+          <t>11813</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>427633</t>
+          <t>427906</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>437966</t>
+          <t>437618</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>178723</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>180606</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>608742</t>
+          <t>608112</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>618871</t>
+          <t>618861</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9601</t>
+          <t>9733</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25522</t>
+          <t>28532</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7998</t>
+          <t>7919</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11019</t>
+          <t>11584</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28015</t>
+          <t>29805</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>556377</t>
+          <t>553367</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>572298</t>
+          <t>572166</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>271513</t>
+          <t>271592</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>833394</t>
+          <t>831604</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>850390</t>
+          <t>849825</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8051</t>
+          <t>8074</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23363</t>
+          <t>23355</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6830</t>
+          <t>6297</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9560</t>
+          <t>9950</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24867</t>
+          <t>26367</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>307674</t>
+          <t>307682</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>322986</t>
+          <t>322963</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>123519</t>
+          <t>124052</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>436519</t>
+          <t>435019</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>451826</t>
+          <t>451436</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9440</t>
+          <t>9489</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26623</t>
+          <t>25496</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4395</t>
+          <t>4353</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17974</t>
+          <t>18057</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16357</t>
+          <t>16516</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36407</t>
+          <t>36010</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>502026</t>
+          <t>503153</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>519209</t>
+          <t>519160</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>286142</t>
+          <t>286059</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>299721</t>
+          <t>299763</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>796358</t>
+          <t>796755</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>816408</t>
+          <t>816249</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,02%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39191</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69535</t>
+          <t>66093</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6959</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22689</t>
+          <t>22856</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>50238</t>
+          <t>50788</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>82102</t>
+          <t>83364</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1811369</t>
+          <t>1814811</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1841713</t>
+          <t>1841980</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>871892</t>
+          <t>871725</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>887622</t>
+          <t>887473</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2693384</t>
+          <t>2692122</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2725248</t>
+          <t>2724698</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han pensado que deberían beber menos en 2012</t>
+          <t>Población según si han pensado que deberían beber menos en 2012 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19134</t>
+          <t>19008</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40522</t>
+          <t>39310</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>924</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7776</t>
+          <t>8726</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21452</t>
+          <t>21569</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43546</t>
+          <t>43231</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>386745</t>
+          <t>387957</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>408133</t>
+          <t>408259</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>167637</t>
+          <t>166687</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>174485</t>
+          <t>174489</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>559134</t>
+          <t>559449</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>581228</t>
+          <t>581111</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19287</t>
+          <t>19763</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43728</t>
+          <t>42743</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1564</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12553</t>
+          <t>12651</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22981</t>
+          <t>23052</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50363</t>
+          <t>49461</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>548629</t>
+          <t>549614</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>573070</t>
+          <t>572594</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>283907</t>
+          <t>283809</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>295385</t>
+          <t>294896</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>838455</t>
+          <t>839357</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>865837</t>
+          <t>865766</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27012</t>
+          <t>27301</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53060</t>
+          <t>51366</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>994</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9970</t>
+          <t>8866</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31559</t>
+          <t>29754</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59514</t>
+          <t>56678</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>407555</t>
+          <t>409249</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>433603</t>
+          <t>433314</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>197734</t>
+          <t>198838</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>206711</t>
+          <t>206710</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>608804</t>
+          <t>611640</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>636759</t>
+          <t>638564</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,55%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30429</t>
+          <t>30517</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57251</t>
+          <t>57761</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4982</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19227</t>
+          <t>21526</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40293</t>
+          <t>38034</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70448</t>
+          <t>70596</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>503130</t>
+          <t>502620</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>529952</t>
+          <t>529864</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>352004</t>
+          <t>349705</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>366249</t>
+          <t>366161</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>861164</t>
+          <t>861016</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>891319</t>
+          <t>893578</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,92%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>114844</t>
+          <t>115514</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>161660</t>
+          <t>162242</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14266</t>
+          <t>13863</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35088</t>
+          <t>34593</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>136494</t>
+          <t>133873</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>189385</t>
+          <t>187440</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1878959</t>
+          <t>1878377</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1925775</t>
+          <t>1925105</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1015720</t>
+          <t>1016215</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1036542</t>
+          <t>1036945</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2902042</t>
+          <t>2903987</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2954933</t>
+          <t>2957554</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han pensado que deberían beber menos en 2016</t>
+          <t>Población según si han pensado que deberían beber menos en 2016 (tasa de respuesta: 99,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8177</t>
+          <t>8173</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23588</t>
+          <t>22818</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1639</t>
+          <t>1669</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10462</t>
+          <t>10442</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11961</t>
+          <t>11846</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31178</t>
+          <t>29027</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>406142</t>
+          <t>406912</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>421553</t>
+          <t>421557</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>172411</t>
+          <t>172431</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>181234</t>
+          <t>181204</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>581425</t>
+          <t>583576</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>600642</t>
+          <t>600757</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21648</t>
+          <t>21115</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45298</t>
+          <t>45349</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3717</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14513</t>
+          <t>14499</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27588</t>
+          <t>28333</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52855</t>
+          <t>54553</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>527125</t>
+          <t>527074</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>550775</t>
+          <t>551308</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>307750</t>
+          <t>307764</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>318546</t>
+          <t>318490</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>841831</t>
+          <t>840133</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>867098</t>
+          <t>866353</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12388</t>
+          <t>12238</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31234</t>
+          <t>32046</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11280</t>
+          <t>11410</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17373</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>37164</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>394563</t>
+          <t>393751</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>413409</t>
+          <t>413559</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>220920</t>
+          <t>220790</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>230139</t>
+          <t>230152</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>619138</t>
+          <t>620833</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>640624</t>
+          <t>641889</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25723</t>
+          <t>26789</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50095</t>
+          <t>51795</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11323</t>
+          <t>11717</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30158</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43918</t>
+          <t>45265</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75079</t>
+          <t>75703</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>522191</t>
+          <t>520491</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>546563</t>
+          <t>545497</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>378814</t>
+          <t>378972</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>397649</t>
+          <t>397255</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>906179</t>
+          <t>905555</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>937340</t>
+          <t>935993</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,39%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>86191</t>
+          <t>85564</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>129082</t>
+          <t>128607</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27059</t>
+          <t>26546</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51661</t>
+          <t>51518</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>118964</t>
+          <t>117227</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>169567</t>
+          <t>165883</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1871154</t>
+          <t>1871629</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1914045</t>
+          <t>1914672</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1094646</t>
+          <t>1094789</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1119248</t>
+          <t>1119761</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2976976</t>
+          <t>2980660</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3027579</t>
+          <t>3029316</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,27%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han pensado que deberían beber menos en 2023</t>
+          <t>Población según si han pensado que deberían beber menos en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3854</t>
+          <t>3673</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14486</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>674</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6558</t>
+          <t>6081</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6028</t>
+          <t>5623</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17406</t>
+          <t>16285</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>319081</t>
+          <t>319886</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>329713</t>
+          <t>329894</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>153539</t>
+          <t>154016</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>159256</t>
+          <t>159423</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>476259</t>
+          <t>477380</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>487637</t>
+          <t>488042</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17348</t>
+          <t>18032</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42474</t>
+          <t>42150</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>5362</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18076</t>
+          <t>18932</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27011</t>
+          <t>24790</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54313</t>
+          <t>52837</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>434282</t>
+          <t>434606</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>459408</t>
+          <t>458724</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>182806</t>
+          <t>181950</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>195618</t>
+          <t>195520</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>623325</t>
+          <t>624801</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>650627</t>
+          <t>652848</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12692</t>
+          <t>12341</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32250</t>
+          <t>33118</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>963</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23419</t>
+          <t>22719</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10388</t>
+          <t>11374</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47462</t>
+          <t>47379</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>293098</t>
+          <t>292230</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>312656</t>
+          <t>313007</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>352678</t>
+          <t>353378</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>375326</t>
+          <t>375134</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>653983</t>
+          <t>654066</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>691057</t>
+          <t>690071</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30162</t>
+          <t>30079</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57954</t>
+          <t>59864</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1447</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>7481</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33331</t>
+          <t>33540</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62624</t>
+          <t>64393</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>385746</t>
+          <t>383836</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>413538</t>
+          <t>413621</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>282522</t>
+          <t>282101</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>288135</t>
+          <t>288097</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>670657</t>
+          <t>668888</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>699950</t>
+          <t>699741</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,43%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>76577</t>
+          <t>77979</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>120635</t>
+          <t>121734</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12219</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37688</t>
+          <t>37468</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93260</t>
+          <t>93197</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>150209</t>
+          <t>150627</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1458736</t>
+          <t>1457637</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1502794</t>
+          <t>1501392</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>988971</t>
+          <t>989191</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1014440</t>
+          <t>1014166</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2455820</t>
+          <t>2455402</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2512769</t>
+          <t>2512832</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/P32-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P32-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>917</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11413</t>
+          <t>11137</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11813</t>
+          <t>12337</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>427906</t>
+          <t>428182</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>437618</t>
+          <t>438402</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>608112</t>
+          <t>607588</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>618861</t>
+          <t>618192</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9733</t>
+          <t>9958</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28532</t>
+          <t>27982</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7919</t>
+          <t>6765</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11584</t>
+          <t>11145</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29805</t>
+          <t>29453</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>553367</t>
+          <t>553917</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>572166</t>
+          <t>571941</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>271592</t>
+          <t>272746</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>831604</t>
+          <t>831956</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>849825</t>
+          <t>850264</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8074</t>
+          <t>7922</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23355</t>
+          <t>23513</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6297</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9950</t>
+          <t>9795</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26367</t>
+          <t>25787</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>307682</t>
+          <t>307524</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>322963</t>
+          <t>323115</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>124052</t>
+          <t>123074</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>435019</t>
+          <t>435599</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>451436</t>
+          <t>451591</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9489</t>
+          <t>9189</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25496</t>
+          <t>25447</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4353</t>
+          <t>3619</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18057</t>
+          <t>16905</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16516</t>
+          <t>16361</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36010</t>
+          <t>37813</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>503153</t>
+          <t>503202</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>519160</t>
+          <t>519460</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>286059</t>
+          <t>287211</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>299763</t>
+          <t>300497</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>796755</t>
+          <t>794952</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>816249</t>
+          <t>816404</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>39033</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66093</t>
+          <t>67920</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7108</t>
+          <t>7166</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22856</t>
+          <t>22250</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>50788</t>
+          <t>49996</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83364</t>
+          <t>81576</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1814811</t>
+          <t>1812984</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1841980</t>
+          <t>1841871</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>871725</t>
+          <t>872331</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>887473</t>
+          <t>887415</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2692122</t>
+          <t>2693910</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2724698</t>
+          <t>2725490</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19008</t>
+          <t>19414</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39310</t>
+          <t>39826</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>934</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8726</t>
+          <t>7919</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21569</t>
+          <t>21234</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43231</t>
+          <t>42055</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>387957</t>
+          <t>387441</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>408259</t>
+          <t>407853</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>166687</t>
+          <t>167494</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>174489</t>
+          <t>174479</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>559449</t>
+          <t>560625</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>581111</t>
+          <t>581446</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,48%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19763</t>
+          <t>20085</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42743</t>
+          <t>42214</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1564</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12651</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23052</t>
+          <t>23509</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49461</t>
+          <t>48843</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>549614</t>
+          <t>550143</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>572594</t>
+          <t>572272</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>283809</t>
+          <t>284406</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>294896</t>
+          <t>295390</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>839357</t>
+          <t>839975</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>865766</t>
+          <t>865309</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27301</t>
+          <t>27699</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51366</t>
+          <t>53695</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>984</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8866</t>
+          <t>9195</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29754</t>
+          <t>30833</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56678</t>
+          <t>56926</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>409249</t>
+          <t>406920</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>433314</t>
+          <t>432916</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>198838</t>
+          <t>198509</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>206710</t>
+          <t>206720</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>611640</t>
+          <t>611392</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>638564</t>
+          <t>637485</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,39%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30517</t>
+          <t>30075</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57761</t>
+          <t>55701</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>4611</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21526</t>
+          <t>19503</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38034</t>
+          <t>37997</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70596</t>
+          <t>69092</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>502620</t>
+          <t>504680</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>529864</t>
+          <t>530306</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>349705</t>
+          <t>351728</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>366161</t>
+          <t>366620</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>861016</t>
+          <t>862520</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>893578</t>
+          <t>893615</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>115514</t>
+          <t>114463</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>162242</t>
+          <t>163599</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13863</t>
+          <t>13739</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34593</t>
+          <t>35819</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>133873</t>
+          <t>135889</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>187440</t>
+          <t>185844</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1878377</t>
+          <t>1877020</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1925105</t>
+          <t>1926156</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1016215</t>
+          <t>1014989</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1036945</t>
+          <t>1037069</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2903987</t>
+          <t>2905583</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2957554</t>
+          <t>2955538</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8173</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22818</t>
+          <t>23777</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10442</t>
+          <t>9762</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11846</t>
+          <t>11892</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29027</t>
+          <t>28648</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>406912</t>
+          <t>405953</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>421557</t>
+          <t>421531</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>172431</t>
+          <t>173111</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>181204</t>
+          <t>181220</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>583576</t>
+          <t>583955</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>600757</t>
+          <t>600711</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21115</t>
+          <t>20569</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45349</t>
+          <t>44821</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3773</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14499</t>
+          <t>15043</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28333</t>
+          <t>27253</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54553</t>
+          <t>54937</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>527074</t>
+          <t>527602</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>551308</t>
+          <t>551854</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>307764</t>
+          <t>307220</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>318490</t>
+          <t>318528</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>840133</t>
+          <t>839749</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>866353</t>
+          <t>867433</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12238</t>
+          <t>12629</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32046</t>
+          <t>32291</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11410</t>
+          <t>12087</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16108</t>
+          <t>16689</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37164</t>
+          <t>37035</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>393751</t>
+          <t>393506</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>413559</t>
+          <t>413168</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>220790</t>
+          <t>220113</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>230152</t>
+          <t>230154</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>620833</t>
+          <t>620962</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>641889</t>
+          <t>641308</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,46%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26789</t>
+          <t>26821</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51795</t>
+          <t>51115</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11717</t>
+          <t>12825</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>30954</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45265</t>
+          <t>42919</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75703</t>
+          <t>73800</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>520491</t>
+          <t>521171</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>545497</t>
+          <t>545465</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>378972</t>
+          <t>378018</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>397255</t>
+          <t>396147</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>905555</t>
+          <t>907458</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>935993</t>
+          <t>938339</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,63%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>85564</t>
+          <t>86421</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>128607</t>
+          <t>127534</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26546</t>
+          <t>27421</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51518</t>
+          <t>51923</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>117227</t>
+          <t>120909</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>165883</t>
+          <t>168154</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1871629</t>
+          <t>1872702</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1914672</t>
+          <t>1913815</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1094789</t>
+          <t>1094384</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1119761</t>
+          <t>1118886</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2980660</t>
+          <t>2978389</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3029316</t>
+          <t>3025634</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -6569,22 +6569,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7636</t>
+          <t>7718</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>3889</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13681</t>
+          <t>13673</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2581</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>860</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6081</t>
+          <t>6629</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>10217</t>
+          <t>10348</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5623</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16285</t>
+          <t>16892</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -6682,27 +6682,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>325931</t>
+          <t>346221</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>319886</t>
+          <t>340266</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>329894</t>
+          <t>350050</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>157516</t>
+          <t>170452</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>154016</t>
+          <t>166453</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>159423</t>
+          <t>172222</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>483448</t>
+          <t>516672</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>477380</t>
+          <t>510128</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>488042</t>
+          <t>521474</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>333567</t>
+          <t>353939</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>333567</t>
+          <t>353939</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>333567</t>
+          <t>353939</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>160097</t>
+          <t>173082</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>160097</t>
+          <t>173082</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>160097</t>
+          <t>173082</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>493665</t>
+          <t>527020</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>493665</t>
+          <t>527020</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>493665</t>
+          <t>527020</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,69 +6912,69 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27337</t>
+          <t>29296</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18032</t>
+          <t>18679</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42150</t>
+          <t>44141</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>8,82%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>11512</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>6099</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>19736</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>5,16%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
           <t>8,84%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>9966</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>5362</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>18932</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,96%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>9,42%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>39</t>
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>37303</t>
+          <t>40808</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24790</t>
+          <t>29396</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52837</t>
+          <t>57567</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -7025,67 +7025,67 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>449419</t>
+          <t>471427</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>434606</t>
+          <t>456582</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>458724</t>
+          <t>482044</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>91,18%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,27%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>211671</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>203447</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>217084</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>94,84%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
           <t>91,16%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,22%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>190916</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>181950</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>195520</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,04%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>90,58%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>640335</t>
+          <t>683098</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>624801</t>
+          <t>666339</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>652848</t>
+          <t>694510</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>95,94%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>476756</t>
+          <t>500723</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>476756</t>
+          <t>500723</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>476756</t>
+          <t>500723</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>200882</t>
+          <t>223183</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>200882</t>
+          <t>223183</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>200882</t>
+          <t>223183</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>677638</t>
+          <t>723906</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>677638</t>
+          <t>723906</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>677638</t>
+          <t>723906</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20523</t>
+          <t>27650</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12341</t>
+          <t>17871</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33118</t>
+          <t>41994</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>11232</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22719</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>28897</t>
+          <t>38882</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11374</t>
+          <t>26641</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47379</t>
+          <t>54165</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>304825</t>
+          <t>332533</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>292230</t>
+          <t>318189</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>313007</t>
+          <t>342312</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>367723</t>
+          <t>189902</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>353378</t>
+          <t>180101</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>375134</t>
+          <t>195897</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>672548</t>
+          <t>522435</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>654066</t>
+          <t>507152</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>690071</t>
+          <t>534676</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>95,25%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>325348</t>
+          <t>360183</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>325348</t>
+          <t>360183</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>325348</t>
+          <t>360183</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>376097</t>
+          <t>201134</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>376097</t>
+          <t>201134</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>376097</t>
+          <t>201134</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>701445</t>
+          <t>561317</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>701445</t>
+          <t>561317</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>701445</t>
+          <t>561317</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>42240</t>
+          <t>44522</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30079</t>
+          <t>32214</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59864</t>
+          <t>64083</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3566</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1485</t>
+          <t>2307</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7481</t>
+          <t>15499</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>45805</t>
+          <t>50395</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33540</t>
+          <t>36731</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64393</t>
+          <t>68632</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>401460</t>
+          <t>421142</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>383836</t>
+          <t>401581</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>413621</t>
+          <t>433450</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>286016</t>
+          <t>302757</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>282101</t>
+          <t>293131</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>288097</t>
+          <t>306323</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>687476</t>
+          <t>723899</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>668888</t>
+          <t>705662</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>699741</t>
+          <t>737563</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,26%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>443700</t>
+          <t>465664</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>443700</t>
+          <t>465664</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>443700</t>
+          <t>465664</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>289582</t>
+          <t>308630</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>289582</t>
+          <t>308630</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>289582</t>
+          <t>308630</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>733281</t>
+          <t>774294</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>733281</t>
+          <t>774294</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>733281</t>
+          <t>774294</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>97735</t>
+          <t>109186</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>77979</t>
+          <t>87427</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>121734</t>
+          <t>134739</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>24487</t>
+          <t>31247</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>21744</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37468</t>
+          <t>45524</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>122222</t>
+          <t>140433</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93197</t>
+          <t>118684</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>150627</t>
+          <t>169199</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1481636</t>
+          <t>1571323</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1457637</t>
+          <t>1545770</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1501392</t>
+          <t>1593082</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1002172</t>
+          <t>874782</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>989191</t>
+          <t>860505</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1014166</t>
+          <t>884285</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2483807</t>
+          <t>2446105</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2455402</t>
+          <t>2417339</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2512832</t>
+          <t>2467854</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>95,41%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1579371</t>
+          <t>1680509</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1579371</t>
+          <t>1680509</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1579371</t>
+          <t>1680509</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1026659</t>
+          <t>906029</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1026659</t>
+          <t>906029</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1026659</t>
+          <t>906029</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>2606029</t>
+          <t>2586538</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2606029</t>
+          <t>2586538</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2606029</t>
+          <t>2586538</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
